--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2020 年 9 月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以 7,000 万元、3,000 万元和1,500万元认购发行人新增注册资本 840万元、360万元和180万元。2020 年 9 月 27 日，经友升股份 2020 年第二次临时股东大会审议通过，友升股份股本由 12,000万元增加至 13,380万元，新增注册资本由金浦临港基金出资 840 万元、金浦科创基金出资 360 万元、上海骁墨出资 180 万元，出资方式均为货币资金，新增股份的认购价格为 8.3333元/股。</t>
+          <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2020 年 9 月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以 7,000 万元、3,000 万元和1,500万元认购发行人新增注册资本 840万元、360万元和180万元。2020 年 9 月 27 日，经友升股份 2020 年第二次临时股东大会审议通过，友升股份股本由 12,000万元增加至 13,380万元，新增注册资本由金浦临港基金出资 840 万元、金浦科创基金出资 360 万元、上海骁墨出资 180 万元，出资方式均为货币资金，新增股份的认购价格为 8.3333元/股。</t>
+          <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2020 年 9 月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以 7,000 万元、3,000 万元和1,500万元认购发行人新增注册资本 840万元、360万元和180万元。2020 年 9 月 27 日，经友升股份 2020 年第二次临时股东大会审议通过，友升股份股本由 12,000万元增加至 13,380万元，新增注册资本由金浦临港基金出资 840 万元、金浦科创基金出资 360 万元、上海骁墨出资 180 万元，出资方式均为货币资金，新增股份的认购价格为 8.3333元/股。</t>
+          <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。</t>
         </is>
       </c>
     </row>
@@ -555,14 +555,18 @@
           <t>财投晨源</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>90</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3026.907</v>
+      </c>
       <c r="F5" t="n">
         <v>33.6323</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2022 年 12 月 4 日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333 万元，新增股份的认购价格为 33.6323 元/股，新增股本的认购情况如下：2022年 12月 19日，友升股份召开 2022年第六次临时股东大会，审议通过了前述议案。</t>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
         </is>
       </c>
     </row>
@@ -580,14 +584,18 @@
           <t>深圳达晨创程</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2905.83072</v>
+      </c>
       <c r="F6" t="n">
         <v>33.6323</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2022 年 12 月 4 日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333 万元，新增股份的认购价格为 33.6323 元/股，新增股本的认购情况如下：2022年 12月 19日，友升股份召开 2022年第六次临时股东大会，审议通过了前述议案。</t>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
         </is>
       </c>
     </row>
@@ -605,14 +613,18 @@
           <t>杭州达晨创程</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>51.84</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1743.498432</v>
+      </c>
       <c r="F7" t="n">
         <v>33.6323</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2022 年 12 月 4 日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333 万元，新增股份的认购价格为 33.6323 元/股，新增股本的认购情况如下：2022年 12月 19日，友升股份召开 2022年第六次临时股东大会，审议通过了前述议案。</t>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
         </is>
       </c>
     </row>
@@ -630,14 +642,18 @@
           <t>达晨财智</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1017.040752</v>
+      </c>
       <c r="F8" t="n">
         <v>33.6323</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2022 年 12 月 4 日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333 万元，新增股份的认购价格为 33.6323 元/股，新增股本的认购情况如下：2022年 12月 19日，友升股份召开 2022年第六次临时股东大会，审议通过了前述议案。</t>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
         </is>
       </c>
     </row>
@@ -655,14 +671,18 @@
           <t>财智创赢</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>339.013584</v>
+      </c>
       <c r="F9" t="n">
         <v>33.6323</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2022 年 12 月 4 日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333 万元，新增股份的认购价格为 33.6323 元/股，新增股本的认购情况如下：2022年 12月 19日，友升股份召开 2022年第六次临时股东大会，审议通过了前述议案。</t>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
         </is>
       </c>
     </row>
@@ -680,14 +700,18 @@
           <t>达晨财汇</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>360</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12107.628</v>
+      </c>
       <c r="F10" t="n">
         <v>33.6323</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2022 年 12 月 4 日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333 万元，新增股份的认购价格为 33.6323 元/股，新增股本的认购情况如下：2022年 12月 19日，友升股份召开 2022年第六次临时股东大会，审议通过了前述议案。</t>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
         </is>
       </c>
     </row>
@@ -705,14 +729,18 @@
           <t>杉晖创业</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>360</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12107.628</v>
+      </c>
       <c r="F11" t="n">
         <v>33.6323</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2022 年 12 月 4 日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333 万元，新增股份的认购价格为 33.6323 元/股，新增股本的认购情况如下：2022年 12月 19日，友升股份召开 2022年第六次临时股东大会，审议通过了前述议案。</t>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
         </is>
       </c>
     </row>
@@ -730,14 +758,18 @@
           <t>杉创智至</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>72</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2421.5256</v>
+      </c>
       <c r="F12" t="n">
         <v>33.6323</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2022 年 12 月 4 日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333 万元，新增股份的认购价格为 33.6323 元/股，新增股本的认购情况如下：2022年 12月 19日，友升股份召开 2022年第六次临时股东大会，审议通过了前述议案。</t>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
         </is>
       </c>
     </row>
@@ -755,14 +787,18 @@
           <t>上海联炻</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2017.938</v>
+      </c>
       <c r="F13" t="n">
         <v>33.6323</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2022 年 12 月 4 日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333 万元，新增股份的认购价格为 33.6323 元/股，新增股本的认购情况如下：2022年 12月 19日，友升股份召开 2022年第六次临时股东大会，审议通过了前述议案。</t>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
         </is>
       </c>
     </row>
@@ -780,14 +816,18 @@
           <t>安吉璞颉</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>60</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2017.938</v>
+      </c>
       <c r="F14" t="n">
         <v>33.6323</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2022 年 12 月 4 日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333 万元，新增股份的认购价格为 33.6323 元/股，新增股本的认购情况如下：2022年 12月 19日，友升股份召开 2022年第六次临时股东大会，审议通过了前述议案。</t>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
         </is>
       </c>
     </row>
@@ -872,14 +912,18 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>12000</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>泽升贸易</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>8976</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
@@ -902,14 +946,18 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>12000</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>罗世兵</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>204</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
@@ -932,14 +980,18 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>12000</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>共青城泽升</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>1020</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
@@ -962,14 +1014,18 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>12000</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>1800</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
@@ -988,7 +1044,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2020年9月整体变更设立股份有限公司后股权结构</t>
+          <t>2020年9月整体变更后股权结构</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1022,7 +1078,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2020年9月整体变更设立股份有限公司后股权结构</t>
+          <t>2020年9月整体变更后股权结构</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1056,7 +1112,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2020年9月整体变更设立股份有限公司后股权结构</t>
+          <t>2020年9月整体变更后股权结构</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1090,7 +1146,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2020年9月整体变更设立股份有限公司后股权结构</t>
+          <t>2020年9月整体变更后股权结构</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1612,7 +1668,9 @@
           <t>财投晨源</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>90</v>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
@@ -1644,7 +1702,9 @@
           <t>深圳达晨创程</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>86.40000000000001</v>
+      </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
@@ -1676,7 +1736,9 @@
           <t>杭州达晨创程</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>51.84</v>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
@@ -1708,7 +1770,9 @@
           <t>达晨财智</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>30.24</v>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
@@ -1740,7 +1804,9 @@
           <t>财智创赢</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>10.08</v>
+      </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
@@ -1772,7 +1838,9 @@
           <t>达晨财汇</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>360</v>
+      </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
@@ -1804,7 +1872,9 @@
           <t>杉晖创业</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>360</v>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
@@ -1836,7 +1906,9 @@
           <t>杉创智至</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>72</v>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
@@ -1868,7 +1940,9 @@
           <t>上海联炻</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>60</v>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
@@ -1900,7 +1974,9 @@
           <t>安吉璞颉</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>60</v>
+      </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。</t>
+          <t>金浦临港基金以7000万元认购新增注册资本840万元</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。</t>
+          <t>金浦科创基金以3000万元认购新增注册资本360万元</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。</t>
+          <t>上海骁墨以1500万元认购新增注册资本180万元</t>
         </is>
       </c>
     </row>
@@ -552,21 +552,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>财投晨源</t>
+          <t>杉晖创业</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>90</v>
+        <v>297.3333</v>
       </c>
       <c r="E5" t="n">
-        <v>3026.907</v>
+        <v>10000</v>
       </c>
       <c r="F5" t="n">
         <v>33.6323</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
+          <t>杉晖创业认购297.3333万股且认购金额10000万元</t>
         </is>
       </c>
     </row>
@@ -581,21 +581,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>深圳达晨创程</t>
+          <t>上海联炻</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>86.40000000000001</v>
+        <v>297.3333</v>
       </c>
       <c r="E6" t="n">
-        <v>2905.83072</v>
+        <v>10000</v>
       </c>
       <c r="F6" t="n">
         <v>33.6323</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
+          <t>上海联炻认购297.3333万股且认购金额10000万元</t>
         </is>
       </c>
     </row>
@@ -610,21 +610,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州达晨创程</t>
+          <t>安吉璞颉</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>51.84</v>
+        <v>148.6667</v>
       </c>
       <c r="E7" t="n">
-        <v>1743.498432</v>
+        <v>5000</v>
       </c>
       <c r="F7" t="n">
         <v>33.6323</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
+          <t>安吉璞颉认购148.6667万股且认购金额5000万元</t>
         </is>
       </c>
     </row>
@@ -639,21 +639,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>达晨财智</t>
+          <t>财投晨源</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>30.24</v>
+        <v>89.2</v>
       </c>
       <c r="E8" t="n">
-        <v>1017.040752</v>
+        <v>3000</v>
       </c>
       <c r="F8" t="n">
         <v>33.6323</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
+          <t>财投晨源认购89.2000万股且认购金额3000万元</t>
         </is>
       </c>
     </row>
@@ -668,21 +668,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>财智创赢</t>
+          <t>深圳达晨创程</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.08</v>
+        <v>86.5984</v>
       </c>
       <c r="E9" t="n">
-        <v>339.013584</v>
+        <v>2912.5</v>
       </c>
       <c r="F9" t="n">
         <v>33.6323</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
+          <t>深圳达晨创程认购86.5984万股且认购金额2912.50万元</t>
         </is>
       </c>
     </row>
@@ -697,21 +697,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>达晨财汇</t>
+          <t>杉创智至</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>360</v>
+        <v>59.4667</v>
       </c>
       <c r="E10" t="n">
-        <v>12107.628</v>
+        <v>2000</v>
       </c>
       <c r="F10" t="n">
         <v>33.6323</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
+          <t>杉创智至认购59.4667万股且认购金额2000万元</t>
         </is>
       </c>
     </row>
@@ -726,21 +726,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杉晖创业</t>
+          <t>杭州达晨创程</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>360</v>
+        <v>51.959</v>
       </c>
       <c r="E11" t="n">
-        <v>12107.628</v>
+        <v>1747.5</v>
       </c>
       <c r="F11" t="n">
         <v>33.6323</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
+          <t>杭州达晨创程认购51.9590万股且认购金额1747.50万元</t>
         </is>
       </c>
     </row>
@@ -755,21 +755,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杉创智至</t>
+          <t>达晨财汇</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>29.7333</v>
       </c>
       <c r="E12" t="n">
-        <v>2421.5256</v>
+        <v>1000</v>
       </c>
       <c r="F12" t="n">
         <v>33.6323</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
+          <t>达晨财汇认购29.7333万股且认购金额1000万元</t>
         </is>
       </c>
     </row>
@@ -784,21 +784,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海联炻</t>
+          <t>达晨财智</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>29.7333</v>
       </c>
       <c r="E13" t="n">
-        <v>2017.938</v>
+        <v>1000</v>
       </c>
       <c r="F13" t="n">
         <v>33.6323</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
+          <t>达晨财智认购29.7333万股且认购金额1000万元</t>
         </is>
       </c>
     </row>
@@ -813,21 +813,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>安吉璞颉</t>
+          <t>财智创赢</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>10.1093</v>
       </c>
       <c r="E14" t="n">
-        <v>2017.938</v>
+        <v>340</v>
       </c>
       <c r="F14" t="n">
         <v>33.6323</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，审议通过了《关于上海友升铝业股份有限公司增资的议案》，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股，新增股本的认购情况如下：</t>
+          <t>财智创赢认购10.1093万股且认购金额340万元</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,17 +903,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>t0｜报告期初</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>报告期初公司股权结构</t>
+          <t>报告期初公司的股权结构</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>12000</v>
+        <v>10950.2788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -922,12 +922,16 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>8976</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>8190.8086</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>74.80%</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>报告期初，友升有限的股权结构如下：</t>
+          <t>报告期初公司的股权结构</t>
         </is>
       </c>
     </row>
@@ -937,31 +941,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>t0｜报告期初</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>报告期初公司股权结构</t>
+          <t>报告期初公司的股权结构</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>12000</v>
+        <v>10950.2788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>达晨创联基金</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>204</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>1642.5418</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15.00%</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>报告期初，友升有限的股权结构如下：</t>
+          <t>报告期初公司的股权结构</t>
         </is>
       </c>
     </row>
@@ -971,17 +979,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>t0｜报告期初</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>报告期初公司股权结构</t>
+          <t>报告期初公司的股权结构</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>12000</v>
+        <v>10950.2788</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,12 +998,16 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>1020</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>930.7737</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8.50%</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>报告期初，友升有限的股权结构如下：</t>
+          <t>报告期初公司的股权结构</t>
         </is>
       </c>
     </row>
@@ -1005,50 +1017,54 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>t0｜报告期初</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>报告期初公司股权结构</t>
+          <t>报告期初公司的股权结构</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>12000</v>
+        <v>10950.2788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>达晨创联基金</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>186.1547</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>报告期初，友升有限的股权结构如下：</t>
+          <t>报告期初公司的股权结构</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t1｜2020-09-30增资后</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2020年9月整体变更后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12000</v>
+        <v>13380</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
@@ -1060,63 +1076,71 @@
         <v>8976</v>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>67.09%</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>公司整体变更设立时的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t1｜2020-09-30增资后</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2020年9月整体变更后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12000</v>
+        <v>13380</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>达晨创联基金</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>204</v>
+        <v>1800</v>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13.45%</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>公司整体变更设立时的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t1｜2020-09-30增资后</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2020年9月整体变更后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12000</v>
+        <v>13380</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
@@ -1128,44 +1152,52 @@
         <v>1020</v>
       </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7.62%</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>公司整体变更设立时的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t1｜2020-09-30增资后</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2020年9月整体变更后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12000</v>
+        <v>13380</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>达晨创联基金</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1800</v>
+        <v>204</v>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1.52%</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>公司整体变更设立时的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1207,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1｜2020-09-30增资后</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2020年9月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1189,17 +1221,21 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>泽升贸易</t>
+          <t>金浦临港基金</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8976</v>
+        <v>840</v>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6.28%</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1245,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1｜2020-09-30增资后</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2020年9月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1223,17 +1259,21 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>金浦科创基金</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>204</v>
+        <v>360</v>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2.69%</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1283,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t1｜2020-09-30增资后</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2020年9月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1257,153 +1297,173 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>共青城泽升</t>
+          <t>上海骁墨</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1020</v>
+        <v>180</v>
       </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2020年9月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13380</v>
+        <v>14480.1333</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>达晨创联基金</t>
+          <t>泽升贸易</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1800</v>
+        <v>8976</v>
       </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>61.99%</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2020年9月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13380</v>
+        <v>14480.1333</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>金浦临港基金</t>
+          <t>达晨创联基金</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>840</v>
+        <v>1800</v>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12.43%</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2020年9月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13380</v>
+        <v>14480.1333</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>金浦科创基金</t>
+          <t>共青城泽升</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>360</v>
+        <v>1020</v>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7.04%</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2020年9月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13380</v>
+        <v>14480.1333</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>上海骁墨</t>
+          <t>金浦临港基金</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>180</v>
+        <v>840</v>
       </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5.80%</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1473,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2022年12月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1427,17 +1487,21 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>泽升贸易</t>
+          <t>金浦科创基金</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>8976</v>
+        <v>360</v>
       </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2.49%</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1511,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2022年12月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1468,10 +1532,14 @@
         <v>204</v>
       </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.41%</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1549,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2022年12月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1495,17 +1563,21 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>共青城泽升</t>
+          <t>上海骁墨</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1020</v>
+        <v>180</v>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1587,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2022年12月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1529,17 +1601,21 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>达晨创联基金</t>
+          <t>杉晖创业</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1800</v>
+        <v>297.3333</v>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2.05%</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1625,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2022年12月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1563,17 +1639,21 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>金浦临港基金</t>
+          <t>上海联炻</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>840</v>
+        <v>297.3333</v>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2.05%</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1663,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2022年12月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1597,17 +1677,21 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>金浦科创基金</t>
+          <t>安吉璞颉</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>360</v>
+        <v>148.6667</v>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1.03%</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1701,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2022年12月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1631,17 +1715,21 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>上海骁墨</t>
+          <t>财投晨源</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>180</v>
+        <v>89.2</v>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1739,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2022年12月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1665,17 +1753,21 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>财投晨源</t>
+          <t>深圳达晨创程</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>90</v>
+        <v>86.5984</v>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1777,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2022年12月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1699,17 +1791,21 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>深圳达晨创程</t>
+          <t>杉创智至</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>86.40000000000001</v>
+        <v>59.4667</v>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1719,12 +1815,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2022年12月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1737,13 +1833,17 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>51.84</v>
+        <v>51.959</v>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2022年12月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1767,17 +1867,21 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>达晨财智</t>
+          <t>达晨财汇</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>30.24</v>
+        <v>29.7333</v>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1787,12 +1891,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2022年12月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1801,17 +1905,21 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>财智创赢</t>
+          <t>达晨财智</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>10.08</v>
+        <v>29.7333</v>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1929,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t2｜2022-12-19增资后</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2022年12月增资后股权结构</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1835,153 +1943,21 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>达晨财汇</t>
+          <t>财智创赢</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>360</v>
+        <v>10.1093</v>
       </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>45</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>t3</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2022年12月增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>14480.1333</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>杉晖创业</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>360</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>45</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>t3</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2022年12月增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>14480.1333</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>杉创智至</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>72</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>45</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>t3</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2022年12月增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>14480.1333</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>上海联炻</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>60</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>45</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>t3</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2022年12月增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>14480.1333</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>安吉璞颉</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>60</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>本次增资后，友升股份的股权结构如下：</t>
+          <t>本次增资后股权结构如下</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,7 +912,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>10950.2788</v>
       </c>
@@ -920,7 +920,6 @@
           <t>泽升贸易</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>8190.8086</v>
       </c>
@@ -949,7 +948,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>10950.2788</v>
       </c>
@@ -958,7 +956,6 @@
           <t>达晨创联基金</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1642.5418</v>
       </c>
@@ -987,7 +984,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>10950.2788</v>
       </c>
@@ -996,7 +992,6 @@
           <t>共青城泽升</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>930.7737</v>
       </c>
@@ -1025,7 +1020,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>10950.2788</v>
       </c>
@@ -1034,7 +1028,6 @@
           <t>罗世兵</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>186.1547</v>
       </c>
@@ -1066,7 +1059,6 @@
       <c r="D6" t="n">
         <v>13380</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1075,7 +1067,6 @@
       <c r="G6" t="n">
         <v>8976</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>67.09%</t>
@@ -1104,7 +1095,6 @@
       <c r="D7" t="n">
         <v>13380</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1113,7 +1103,6 @@
       <c r="G7" t="n">
         <v>1800</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>13.45%</t>
@@ -1142,7 +1131,6 @@
       <c r="D8" t="n">
         <v>13380</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1151,7 +1139,6 @@
       <c r="G8" t="n">
         <v>1020</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>7.62%</t>
@@ -1180,7 +1167,6 @@
       <c r="D9" t="n">
         <v>13380</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1189,7 +1175,6 @@
       <c r="G9" t="n">
         <v>204</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>1.52%</t>
@@ -1218,7 +1203,6 @@
       <c r="D10" t="n">
         <v>13380</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1227,7 +1211,6 @@
       <c r="G10" t="n">
         <v>840</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>6.28%</t>
@@ -1256,7 +1239,6 @@
       <c r="D11" t="n">
         <v>13380</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1265,7 +1247,6 @@
       <c r="G11" t="n">
         <v>360</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2.69%</t>
@@ -1294,7 +1275,6 @@
       <c r="D12" t="n">
         <v>13380</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1303,7 +1283,6 @@
       <c r="G12" t="n">
         <v>180</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>1.35%</t>
@@ -1332,7 +1311,6 @@
       <c r="D13" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1341,7 +1319,6 @@
       <c r="G13" t="n">
         <v>8976</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>61.99%</t>
@@ -1370,7 +1347,6 @@
       <c r="D14" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1379,7 +1355,6 @@
       <c r="G14" t="n">
         <v>1800</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>12.43%</t>
@@ -1408,7 +1383,6 @@
       <c r="D15" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1417,7 +1391,6 @@
       <c r="G15" t="n">
         <v>1020</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>7.04%</t>
@@ -1446,7 +1419,6 @@
       <c r="D16" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1455,7 +1427,6 @@
       <c r="G16" t="n">
         <v>840</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>5.80%</t>
@@ -1484,7 +1455,6 @@
       <c r="D17" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1493,7 +1463,6 @@
       <c r="G17" t="n">
         <v>360</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2.49%</t>
@@ -1522,7 +1491,6 @@
       <c r="D18" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1531,7 +1499,6 @@
       <c r="G18" t="n">
         <v>204</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>1.41%</t>
@@ -1560,7 +1527,6 @@
       <c r="D19" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1569,7 +1535,6 @@
       <c r="G19" t="n">
         <v>180</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>1.24%</t>
@@ -1598,7 +1563,6 @@
       <c r="D20" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>杉晖创业</t>
@@ -1607,7 +1571,6 @@
       <c r="G20" t="n">
         <v>297.3333</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1636,7 +1599,6 @@
       <c r="D21" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>上海联炻</t>
@@ -1645,7 +1607,6 @@
       <c r="G21" t="n">
         <v>297.3333</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1674,7 +1635,6 @@
       <c r="D22" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>安吉璞颉</t>
@@ -1683,7 +1643,6 @@
       <c r="G22" t="n">
         <v>148.6667</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>1.03%</t>
@@ -1712,7 +1671,6 @@
       <c r="D23" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>财投晨源</t>
@@ -1721,7 +1679,6 @@
       <c r="G23" t="n">
         <v>89.2</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>0.62%</t>
@@ -1750,7 +1707,6 @@
       <c r="D24" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>深圳达晨创程</t>
@@ -1759,7 +1715,6 @@
       <c r="G24" t="n">
         <v>86.5984</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>0.60%</t>
@@ -1788,7 +1743,6 @@
       <c r="D25" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>杉创智至</t>
@@ -1797,7 +1751,6 @@
       <c r="G25" t="n">
         <v>59.4667</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>0.41%</t>
@@ -1826,7 +1779,6 @@
       <c r="D26" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>杭州达晨创程</t>
@@ -1835,7 +1787,6 @@
       <c r="G26" t="n">
         <v>51.959</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>0.36%</t>
@@ -1864,7 +1815,6 @@
       <c r="D27" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>达晨财汇</t>
@@ -1873,7 +1823,6 @@
       <c r="G27" t="n">
         <v>29.7333</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1902,7 +1851,6 @@
       <c r="D28" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>达晨财智</t>
@@ -1911,7 +1859,6 @@
       <c r="G28" t="n">
         <v>29.7333</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1940,7 +1887,6 @@
       <c r="D29" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>财智创赢</t>
@@ -1949,7 +1895,6 @@
       <c r="G29" t="n">
         <v>10.1093</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>0.07%</t>
@@ -1960,6 +1905,1184 @@
           <t>本次增资后股权结构如下</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化(万股)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值(万股)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴流量13条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>股权存量28条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>字段类型+t0存在检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10950.2788</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2480.1333</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13430.4121</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13380</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-50.4121</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13380</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2480.1333</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15860.1333</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14480.1333</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-1380</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上海骁墨</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>180</v>
+      </c>
+      <c r="F6" t="n">
+        <v>180</v>
+      </c>
+      <c r="G6" t="n">
+        <v>180</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>共青城泽升</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>930.7737</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>930.7737</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H7" t="n">
+        <v>89.22629999999999</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>泽升贸易</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8190.8086</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8190.8086</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8976</v>
+      </c>
+      <c r="H8" t="n">
+        <v>785.1914</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>186.1547</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>186.1547</v>
+      </c>
+      <c r="G9" t="n">
+        <v>204</v>
+      </c>
+      <c r="H9" t="n">
+        <v>17.8453</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>达晨创联基金</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1642.5418</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1642.5418</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H10" t="n">
+        <v>157.4582</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>金浦临港基金</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>840</v>
+      </c>
+      <c r="F11" t="n">
+        <v>840</v>
+      </c>
+      <c r="G11" t="n">
+        <v>840</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>金浦科创基金</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>360</v>
+      </c>
+      <c r="F12" t="n">
+        <v>360</v>
+      </c>
+      <c r="G12" t="n">
+        <v>360</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>上海联炻</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="F13" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="G13" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上海骁墨</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>180</v>
+      </c>
+      <c r="E14" t="n">
+        <v>180</v>
+      </c>
+      <c r="F14" t="n">
+        <v>360</v>
+      </c>
+      <c r="G14" t="n">
+        <v>180</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-180</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>共青城泽升</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1020</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>安吉璞颉</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>148.6667</v>
+      </c>
+      <c r="F16" t="n">
+        <v>148.6667</v>
+      </c>
+      <c r="G16" t="n">
+        <v>148.6667</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>杉创智至</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>59.4667</v>
+      </c>
+      <c r="F17" t="n">
+        <v>59.4667</v>
+      </c>
+      <c r="G17" t="n">
+        <v>59.4667</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>杉晖创业</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="F18" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="G18" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>杭州达晨创程</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>51.959</v>
+      </c>
+      <c r="F19" t="n">
+        <v>51.959</v>
+      </c>
+      <c r="G19" t="n">
+        <v>51.959</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>泽升贸易</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>8976</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8976</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8976</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>深圳达晨创程</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>86.5984</v>
+      </c>
+      <c r="F21" t="n">
+        <v>86.5984</v>
+      </c>
+      <c r="G21" t="n">
+        <v>86.5984</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>204</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>204</v>
+      </c>
+      <c r="G22" t="n">
+        <v>204</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>财投晨源</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>财智创赢</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10.1093</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10.1093</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10.1093</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>达晨创联基金</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>达晨财智</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="F26" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="G26" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>达晨财汇</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="F27" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="G27" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>金浦临港基金</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>840</v>
+      </c>
+      <c r="E28" t="n">
+        <v>840</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1680</v>
+      </c>
+      <c r="G28" t="n">
+        <v>840</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-840</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>金浦科创基金</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>360</v>
+      </c>
+      <c r="E29" t="n">
+        <v>360</v>
+      </c>
+      <c r="F29" t="n">
+        <v>720</v>
+      </c>
+      <c r="G29" t="n">
+        <v>360</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-360</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -912,6 +911,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>10950.2788</v>
       </c>
@@ -920,6 +920,7 @@
           <t>泽升贸易</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>8190.8086</v>
       </c>
@@ -948,6 +949,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>10950.2788</v>
       </c>
@@ -956,6 +958,7 @@
           <t>达晨创联基金</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1642.5418</v>
       </c>
@@ -984,6 +987,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>10950.2788</v>
       </c>
@@ -992,6 +996,7 @@
           <t>共青城泽升</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>930.7737</v>
       </c>
@@ -1020,6 +1025,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>10950.2788</v>
       </c>
@@ -1028,6 +1034,7 @@
           <t>罗世兵</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>186.1547</v>
       </c>
@@ -1059,6 +1066,7 @@
       <c r="D6" t="n">
         <v>13380</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1067,6 +1075,7 @@
       <c r="G6" t="n">
         <v>8976</v>
       </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>67.09%</t>
@@ -1095,6 +1104,7 @@
       <c r="D7" t="n">
         <v>13380</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1103,6 +1113,7 @@
       <c r="G7" t="n">
         <v>1800</v>
       </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>13.45%</t>
@@ -1131,6 +1142,7 @@
       <c r="D8" t="n">
         <v>13380</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1139,6 +1151,7 @@
       <c r="G8" t="n">
         <v>1020</v>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>7.62%</t>
@@ -1167,6 +1180,7 @@
       <c r="D9" t="n">
         <v>13380</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1175,6 +1189,7 @@
       <c r="G9" t="n">
         <v>204</v>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>1.52%</t>
@@ -1203,6 +1218,7 @@
       <c r="D10" t="n">
         <v>13380</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1211,6 +1227,7 @@
       <c r="G10" t="n">
         <v>840</v>
       </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>6.28%</t>
@@ -1239,6 +1256,7 @@
       <c r="D11" t="n">
         <v>13380</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1247,6 +1265,7 @@
       <c r="G11" t="n">
         <v>360</v>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2.69%</t>
@@ -1275,6 +1294,7 @@
       <c r="D12" t="n">
         <v>13380</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1283,6 +1303,7 @@
       <c r="G12" t="n">
         <v>180</v>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>1.35%</t>
@@ -1311,6 +1332,7 @@
       <c r="D13" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1319,6 +1341,7 @@
       <c r="G13" t="n">
         <v>8976</v>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>61.99%</t>
@@ -1347,6 +1370,7 @@
       <c r="D14" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1355,6 +1379,7 @@
       <c r="G14" t="n">
         <v>1800</v>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>12.43%</t>
@@ -1383,6 +1408,7 @@
       <c r="D15" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1391,6 +1417,7 @@
       <c r="G15" t="n">
         <v>1020</v>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>7.04%</t>
@@ -1419,6 +1446,7 @@
       <c r="D16" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1427,6 +1455,7 @@
       <c r="G16" t="n">
         <v>840</v>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>5.80%</t>
@@ -1455,6 +1484,7 @@
       <c r="D17" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1463,6 +1493,7 @@
       <c r="G17" t="n">
         <v>360</v>
       </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2.49%</t>
@@ -1491,6 +1522,7 @@
       <c r="D18" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1499,6 +1531,7 @@
       <c r="G18" t="n">
         <v>204</v>
       </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>1.41%</t>
@@ -1527,6 +1560,7 @@
       <c r="D19" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1535,6 +1569,7 @@
       <c r="G19" t="n">
         <v>180</v>
       </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>1.24%</t>
@@ -1563,6 +1598,7 @@
       <c r="D20" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>杉晖创业</t>
@@ -1571,6 +1607,7 @@
       <c r="G20" t="n">
         <v>297.3333</v>
       </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1599,6 +1636,7 @@
       <c r="D21" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>上海联炻</t>
@@ -1607,6 +1645,7 @@
       <c r="G21" t="n">
         <v>297.3333</v>
       </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1635,6 +1674,7 @@
       <c r="D22" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>安吉璞颉</t>
@@ -1643,6 +1683,7 @@
       <c r="G22" t="n">
         <v>148.6667</v>
       </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>1.03%</t>
@@ -1671,6 +1712,7 @@
       <c r="D23" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>财投晨源</t>
@@ -1679,6 +1721,7 @@
       <c r="G23" t="n">
         <v>89.2</v>
       </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>0.62%</t>
@@ -1707,6 +1750,7 @@
       <c r="D24" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>深圳达晨创程</t>
@@ -1715,6 +1759,7 @@
       <c r="G24" t="n">
         <v>86.5984</v>
       </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>0.60%</t>
@@ -1743,6 +1788,7 @@
       <c r="D25" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>杉创智至</t>
@@ -1751,6 +1797,7 @@
       <c r="G25" t="n">
         <v>59.4667</v>
       </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>0.41%</t>
@@ -1779,6 +1826,7 @@
       <c r="D26" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>杭州达晨创程</t>
@@ -1787,6 +1835,7 @@
       <c r="G26" t="n">
         <v>51.959</v>
       </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>0.36%</t>
@@ -1815,6 +1864,7 @@
       <c r="D27" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>达晨财汇</t>
@@ -1823,6 +1873,7 @@
       <c r="G27" t="n">
         <v>29.7333</v>
       </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1851,6 +1902,7 @@
       <c r="D28" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>达晨财智</t>
@@ -1859,6 +1911,7 @@
       <c r="G28" t="n">
         <v>29.7333</v>
       </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1887,6 +1940,7 @@
       <c r="D29" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>财智创赢</t>
@@ -1895,6 +1949,7 @@
       <c r="G29" t="n">
         <v>10.1093</v>
       </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>0.07%</t>
@@ -1905,1184 +1960,6 @@
           <t>本次增资后股权结构如下</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化(万股)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值(万股)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴流量13条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>股权存量28条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>字段类型+t0存在检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10950.2788</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2480.1333</v>
-      </c>
-      <c r="F4" t="n">
-        <v>13430.4121</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13380</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-50.4121</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>13380</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2480.1333</v>
-      </c>
-      <c r="F5" t="n">
-        <v>15860.1333</v>
-      </c>
-      <c r="G5" t="n">
-        <v>14480.1333</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-1380</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>上海骁墨</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>180</v>
-      </c>
-      <c r="F6" t="n">
-        <v>180</v>
-      </c>
-      <c r="G6" t="n">
-        <v>180</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>共青城泽升</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>930.7737</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>930.7737</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1020</v>
-      </c>
-      <c r="H7" t="n">
-        <v>89.22629999999999</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>泽升贸易</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>8190.8086</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8190.8086</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8976</v>
-      </c>
-      <c r="H8" t="n">
-        <v>785.1914</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>186.1547</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>186.1547</v>
-      </c>
-      <c r="G9" t="n">
-        <v>204</v>
-      </c>
-      <c r="H9" t="n">
-        <v>17.8453</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>达晨创联基金</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1642.5418</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1642.5418</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H10" t="n">
-        <v>157.4582</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>金浦临港基金</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>840</v>
-      </c>
-      <c r="F11" t="n">
-        <v>840</v>
-      </c>
-      <c r="G11" t="n">
-        <v>840</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>金浦科创基金</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>360</v>
-      </c>
-      <c r="F12" t="n">
-        <v>360</v>
-      </c>
-      <c r="G12" t="n">
-        <v>360</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>上海联炻</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="F13" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="G13" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>上海骁墨</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>180</v>
-      </c>
-      <c r="E14" t="n">
-        <v>180</v>
-      </c>
-      <c r="F14" t="n">
-        <v>360</v>
-      </c>
-      <c r="G14" t="n">
-        <v>180</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-180</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>共青城泽升</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1020</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1020</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>安吉璞颉</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>148.6667</v>
-      </c>
-      <c r="F16" t="n">
-        <v>148.6667</v>
-      </c>
-      <c r="G16" t="n">
-        <v>148.6667</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>杉创智至</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>59.4667</v>
-      </c>
-      <c r="F17" t="n">
-        <v>59.4667</v>
-      </c>
-      <c r="G17" t="n">
-        <v>59.4667</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>杉晖创业</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="F18" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="G18" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>杭州达晨创程</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>51.959</v>
-      </c>
-      <c r="F19" t="n">
-        <v>51.959</v>
-      </c>
-      <c r="G19" t="n">
-        <v>51.959</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>泽升贸易</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>8976</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>8976</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8976</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>深圳达晨创程</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>86.5984</v>
-      </c>
-      <c r="F21" t="n">
-        <v>86.5984</v>
-      </c>
-      <c r="G21" t="n">
-        <v>86.5984</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>204</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>204</v>
-      </c>
-      <c r="G22" t="n">
-        <v>204</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>财投晨源</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="G23" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>财智创赢</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>10.1093</v>
-      </c>
-      <c r="F24" t="n">
-        <v>10.1093</v>
-      </c>
-      <c r="G24" t="n">
-        <v>10.1093</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>达晨创联基金</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>达晨财智</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="F26" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="G26" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>达晨财汇</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="F27" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="G27" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>金浦临港基金</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>840</v>
-      </c>
-      <c r="E28" t="n">
-        <v>840</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1680</v>
-      </c>
-      <c r="G28" t="n">
-        <v>840</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-840</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>金浦科创基金</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>360</v>
-      </c>
-      <c r="E29" t="n">
-        <v>360</v>
-      </c>
-      <c r="F29" t="n">
-        <v>720</v>
-      </c>
-      <c r="G29" t="n">
-        <v>360</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-360</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,7 +912,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>10950.2788</v>
       </c>
@@ -920,7 +920,6 @@
           <t>泽升贸易</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>8190.8086</v>
       </c>
@@ -949,7 +948,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>10950.2788</v>
       </c>
@@ -958,7 +956,6 @@
           <t>达晨创联基金</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1642.5418</v>
       </c>
@@ -987,7 +984,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>10950.2788</v>
       </c>
@@ -996,7 +992,6 @@
           <t>共青城泽升</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>930.7737</v>
       </c>
@@ -1025,7 +1020,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>10950.2788</v>
       </c>
@@ -1034,7 +1028,6 @@
           <t>罗世兵</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>186.1547</v>
       </c>
@@ -1066,7 +1059,6 @@
       <c r="D6" t="n">
         <v>13380</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1075,7 +1067,6 @@
       <c r="G6" t="n">
         <v>8976</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>67.09%</t>
@@ -1104,7 +1095,6 @@
       <c r="D7" t="n">
         <v>13380</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1113,7 +1103,6 @@
       <c r="G7" t="n">
         <v>1800</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>13.45%</t>
@@ -1142,7 +1131,6 @@
       <c r="D8" t="n">
         <v>13380</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1151,7 +1139,6 @@
       <c r="G8" t="n">
         <v>1020</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>7.62%</t>
@@ -1180,7 +1167,6 @@
       <c r="D9" t="n">
         <v>13380</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1189,7 +1175,6 @@
       <c r="G9" t="n">
         <v>204</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>1.52%</t>
@@ -1218,7 +1203,6 @@
       <c r="D10" t="n">
         <v>13380</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1227,7 +1211,6 @@
       <c r="G10" t="n">
         <v>840</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>6.28%</t>
@@ -1256,7 +1239,6 @@
       <c r="D11" t="n">
         <v>13380</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1265,7 +1247,6 @@
       <c r="G11" t="n">
         <v>360</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2.69%</t>
@@ -1294,7 +1275,6 @@
       <c r="D12" t="n">
         <v>13380</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1303,7 +1283,6 @@
       <c r="G12" t="n">
         <v>180</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>1.35%</t>
@@ -1332,7 +1311,6 @@
       <c r="D13" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1341,7 +1319,6 @@
       <c r="G13" t="n">
         <v>8976</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>61.99%</t>
@@ -1370,7 +1347,6 @@
       <c r="D14" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1379,7 +1355,6 @@
       <c r="G14" t="n">
         <v>1800</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>12.43%</t>
@@ -1408,7 +1383,6 @@
       <c r="D15" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1417,7 +1391,6 @@
       <c r="G15" t="n">
         <v>1020</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>7.04%</t>
@@ -1446,7 +1419,6 @@
       <c r="D16" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1455,7 +1427,6 @@
       <c r="G16" t="n">
         <v>840</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>5.80%</t>
@@ -1484,7 +1455,6 @@
       <c r="D17" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1493,7 +1463,6 @@
       <c r="G17" t="n">
         <v>360</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2.49%</t>
@@ -1522,7 +1491,6 @@
       <c r="D18" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1531,7 +1499,6 @@
       <c r="G18" t="n">
         <v>204</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>1.41%</t>
@@ -1560,7 +1527,6 @@
       <c r="D19" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1569,7 +1535,6 @@
       <c r="G19" t="n">
         <v>180</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>1.24%</t>
@@ -1598,7 +1563,6 @@
       <c r="D20" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>杉晖创业</t>
@@ -1607,7 +1571,6 @@
       <c r="G20" t="n">
         <v>297.3333</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1636,7 +1599,6 @@
       <c r="D21" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>上海联炻</t>
@@ -1645,7 +1607,6 @@
       <c r="G21" t="n">
         <v>297.3333</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1674,7 +1635,6 @@
       <c r="D22" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>安吉璞颉</t>
@@ -1683,7 +1643,6 @@
       <c r="G22" t="n">
         <v>148.6667</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>1.03%</t>
@@ -1712,7 +1671,6 @@
       <c r="D23" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>财投晨源</t>
@@ -1721,7 +1679,6 @@
       <c r="G23" t="n">
         <v>89.2</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>0.62%</t>
@@ -1750,7 +1707,6 @@
       <c r="D24" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>深圳达晨创程</t>
@@ -1759,7 +1715,6 @@
       <c r="G24" t="n">
         <v>86.5984</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>0.60%</t>
@@ -1788,7 +1743,6 @@
       <c r="D25" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>杉创智至</t>
@@ -1797,7 +1751,6 @@
       <c r="G25" t="n">
         <v>59.4667</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>0.41%</t>
@@ -1826,7 +1779,6 @@
       <c r="D26" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>杭州达晨创程</t>
@@ -1835,7 +1787,6 @@
       <c r="G26" t="n">
         <v>51.959</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>0.36%</t>
@@ -1864,7 +1815,6 @@
       <c r="D27" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>达晨财汇</t>
@@ -1873,7 +1823,6 @@
       <c r="G27" t="n">
         <v>29.7333</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1902,7 +1851,6 @@
       <c r="D28" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>达晨财智</t>
@@ -1911,7 +1859,6 @@
       <c r="G28" t="n">
         <v>29.7333</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1940,7 +1887,6 @@
       <c r="D29" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>财智创赢</t>
@@ -1949,7 +1895,6 @@
       <c r="G29" t="n">
         <v>10.1093</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>0.07%</t>
@@ -1960,6 +1905,1168 @@
           <t>本次增资后股权结构如下</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴13条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量28条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10950.2788</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2480.1333</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13430.4121</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13380</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-50.4121</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上海骁墨</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>180</v>
+      </c>
+      <c r="F5" t="n">
+        <v>180</v>
+      </c>
+      <c r="G5" t="n">
+        <v>180</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>共青城泽升</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>930.7737</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>930.7737</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H6" t="n">
+        <v>89.22629999999999</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>泽升贸易</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8190.8086</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8190.8086</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8976</v>
+      </c>
+      <c r="H7" t="n">
+        <v>785.1914</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>186.1547</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>186.1547</v>
+      </c>
+      <c r="G8" t="n">
+        <v>204</v>
+      </c>
+      <c r="H8" t="n">
+        <v>17.8453</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>达晨创联基金</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1642.5418</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1642.5418</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H9" t="n">
+        <v>157.4582</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>金浦临港基金</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>840</v>
+      </c>
+      <c r="F10" t="n">
+        <v>840</v>
+      </c>
+      <c r="G10" t="n">
+        <v>840</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>金浦科创基金</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>360</v>
+      </c>
+      <c r="F11" t="n">
+        <v>360</v>
+      </c>
+      <c r="G11" t="n">
+        <v>360</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13380</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2480.1333</v>
+      </c>
+      <c r="F12" t="n">
+        <v>15860.1333</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14480.1333</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-1380</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>上海联炻</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="F13" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="G13" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上海骁墨</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>180</v>
+      </c>
+      <c r="E14" t="n">
+        <v>180</v>
+      </c>
+      <c r="F14" t="n">
+        <v>360</v>
+      </c>
+      <c r="G14" t="n">
+        <v>180</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-180</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>共青城泽升</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1020</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>安吉璞颉</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>148.6667</v>
+      </c>
+      <c r="F16" t="n">
+        <v>148.6667</v>
+      </c>
+      <c r="G16" t="n">
+        <v>148.6667</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>杉创智至</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>59.4667</v>
+      </c>
+      <c r="F17" t="n">
+        <v>59.4667</v>
+      </c>
+      <c r="G17" t="n">
+        <v>59.4667</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>杉晖创业</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="F18" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="G18" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>杭州达晨创程</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>51.959</v>
+      </c>
+      <c r="F19" t="n">
+        <v>51.959</v>
+      </c>
+      <c r="G19" t="n">
+        <v>51.959</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>泽升贸易</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>8976</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8976</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8976</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>深圳达晨创程</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>86.5984</v>
+      </c>
+      <c r="F21" t="n">
+        <v>86.5984</v>
+      </c>
+      <c r="G21" t="n">
+        <v>86.5984</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>204</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>204</v>
+      </c>
+      <c r="G22" t="n">
+        <v>204</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>财投晨源</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>财智创赢</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10.1093</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10.1093</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10.1093</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>达晨创联基金</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>达晨财智</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="F26" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="G26" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>达晨财汇</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="F27" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="G27" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>金浦临港基金</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>840</v>
+      </c>
+      <c r="E28" t="n">
+        <v>840</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1680</v>
+      </c>
+      <c r="G28" t="n">
+        <v>840</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-840</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>金浦科创基金</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>360</v>
+      </c>
+      <c r="E29" t="n">
+        <v>360</v>
+      </c>
+      <c r="F29" t="n">
+        <v>720</v>
+      </c>
+      <c r="G29" t="n">
+        <v>360</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-360</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -912,6 +911,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>10950.2788</v>
       </c>
@@ -920,6 +920,7 @@
           <t>泽升贸易</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>8190.8086</v>
       </c>
@@ -948,6 +949,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>10950.2788</v>
       </c>
@@ -956,6 +958,7 @@
           <t>达晨创联基金</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1642.5418</v>
       </c>
@@ -984,6 +987,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>10950.2788</v>
       </c>
@@ -992,6 +996,7 @@
           <t>共青城泽升</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>930.7737</v>
       </c>
@@ -1020,6 +1025,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>10950.2788</v>
       </c>
@@ -1028,6 +1034,7 @@
           <t>罗世兵</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>186.1547</v>
       </c>
@@ -1059,6 +1066,7 @@
       <c r="D6" t="n">
         <v>13380</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1067,6 +1075,7 @@
       <c r="G6" t="n">
         <v>8976</v>
       </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>67.09%</t>
@@ -1095,6 +1104,7 @@
       <c r="D7" t="n">
         <v>13380</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1103,6 +1113,7 @@
       <c r="G7" t="n">
         <v>1800</v>
       </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>13.45%</t>
@@ -1131,6 +1142,7 @@
       <c r="D8" t="n">
         <v>13380</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1139,6 +1151,7 @@
       <c r="G8" t="n">
         <v>1020</v>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>7.62%</t>
@@ -1167,6 +1180,7 @@
       <c r="D9" t="n">
         <v>13380</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1175,6 +1189,7 @@
       <c r="G9" t="n">
         <v>204</v>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>1.52%</t>
@@ -1203,6 +1218,7 @@
       <c r="D10" t="n">
         <v>13380</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1211,6 +1227,7 @@
       <c r="G10" t="n">
         <v>840</v>
       </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>6.28%</t>
@@ -1239,6 +1256,7 @@
       <c r="D11" t="n">
         <v>13380</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1247,6 +1265,7 @@
       <c r="G11" t="n">
         <v>360</v>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2.69%</t>
@@ -1275,6 +1294,7 @@
       <c r="D12" t="n">
         <v>13380</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1283,6 +1303,7 @@
       <c r="G12" t="n">
         <v>180</v>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>1.35%</t>
@@ -1311,6 +1332,7 @@
       <c r="D13" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1319,6 +1341,7 @@
       <c r="G13" t="n">
         <v>8976</v>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>61.99%</t>
@@ -1347,6 +1370,7 @@
       <c r="D14" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1355,6 +1379,7 @@
       <c r="G14" t="n">
         <v>1800</v>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>12.43%</t>
@@ -1383,6 +1408,7 @@
       <c r="D15" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1391,6 +1417,7 @@
       <c r="G15" t="n">
         <v>1020</v>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>7.04%</t>
@@ -1419,6 +1446,7 @@
       <c r="D16" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1427,6 +1455,7 @@
       <c r="G16" t="n">
         <v>840</v>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>5.80%</t>
@@ -1455,6 +1484,7 @@
       <c r="D17" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1463,6 +1493,7 @@
       <c r="G17" t="n">
         <v>360</v>
       </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2.49%</t>
@@ -1491,6 +1522,7 @@
       <c r="D18" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1499,6 +1531,7 @@
       <c r="G18" t="n">
         <v>204</v>
       </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>1.41%</t>
@@ -1527,6 +1560,7 @@
       <c r="D19" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1535,6 +1569,7 @@
       <c r="G19" t="n">
         <v>180</v>
       </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>1.24%</t>
@@ -1563,6 +1598,7 @@
       <c r="D20" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>杉晖创业</t>
@@ -1571,6 +1607,7 @@
       <c r="G20" t="n">
         <v>297.3333</v>
       </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1599,6 +1636,7 @@
       <c r="D21" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>上海联炻</t>
@@ -1607,6 +1645,7 @@
       <c r="G21" t="n">
         <v>297.3333</v>
       </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1635,6 +1674,7 @@
       <c r="D22" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>安吉璞颉</t>
@@ -1643,6 +1683,7 @@
       <c r="G22" t="n">
         <v>148.6667</v>
       </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>1.03%</t>
@@ -1671,6 +1712,7 @@
       <c r="D23" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>财投晨源</t>
@@ -1679,6 +1721,7 @@
       <c r="G23" t="n">
         <v>89.2</v>
       </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>0.62%</t>
@@ -1707,6 +1750,7 @@
       <c r="D24" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>深圳达晨创程</t>
@@ -1715,6 +1759,7 @@
       <c r="G24" t="n">
         <v>86.5984</v>
       </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>0.60%</t>
@@ -1743,6 +1788,7 @@
       <c r="D25" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>杉创智至</t>
@@ -1751,6 +1797,7 @@
       <c r="G25" t="n">
         <v>59.4667</v>
       </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>0.41%</t>
@@ -1779,6 +1826,7 @@
       <c r="D26" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>杭州达晨创程</t>
@@ -1787,6 +1835,7 @@
       <c r="G26" t="n">
         <v>51.959</v>
       </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>0.36%</t>
@@ -1815,6 +1864,7 @@
       <c r="D27" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>达晨财汇</t>
@@ -1823,6 +1873,7 @@
       <c r="G27" t="n">
         <v>29.7333</v>
       </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1851,6 +1902,7 @@
       <c r="D28" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>达晨财智</t>
@@ -1859,6 +1911,7 @@
       <c r="G28" t="n">
         <v>29.7333</v>
       </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1887,6 +1940,7 @@
       <c r="D29" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>财智创赢</t>
@@ -1895,6 +1949,7 @@
       <c r="G29" t="n">
         <v>10.1093</v>
       </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>0.07%</t>
@@ -1905,1168 +1960,6 @@
           <t>本次增资后股权结构如下</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴13条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量28条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10950.2788</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2480.1333</v>
-      </c>
-      <c r="F4" t="n">
-        <v>13430.4121</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13380</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-50.4121</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>上海骁墨</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>180</v>
-      </c>
-      <c r="F5" t="n">
-        <v>180</v>
-      </c>
-      <c r="G5" t="n">
-        <v>180</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>共青城泽升</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>930.7737</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>930.7737</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1020</v>
-      </c>
-      <c r="H6" t="n">
-        <v>89.22629999999999</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>泽升贸易</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>8190.8086</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8190.8086</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8976</v>
-      </c>
-      <c r="H7" t="n">
-        <v>785.1914</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>186.1547</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>186.1547</v>
-      </c>
-      <c r="G8" t="n">
-        <v>204</v>
-      </c>
-      <c r="H8" t="n">
-        <v>17.8453</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>达晨创联基金</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>1642.5418</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1642.5418</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H9" t="n">
-        <v>157.4582</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>金浦临港基金</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>840</v>
-      </c>
-      <c r="F10" t="n">
-        <v>840</v>
-      </c>
-      <c r="G10" t="n">
-        <v>840</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>金浦科创基金</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>360</v>
-      </c>
-      <c r="F11" t="n">
-        <v>360</v>
-      </c>
-      <c r="G11" t="n">
-        <v>360</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>13380</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2480.1333</v>
-      </c>
-      <c r="F12" t="n">
-        <v>15860.1333</v>
-      </c>
-      <c r="G12" t="n">
-        <v>14480.1333</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-1380</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>上海联炻</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="F13" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="G13" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>上海骁墨</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>180</v>
-      </c>
-      <c r="E14" t="n">
-        <v>180</v>
-      </c>
-      <c r="F14" t="n">
-        <v>360</v>
-      </c>
-      <c r="G14" t="n">
-        <v>180</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-180</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>共青城泽升</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1020</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1020</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>安吉璞颉</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>148.6667</v>
-      </c>
-      <c r="F16" t="n">
-        <v>148.6667</v>
-      </c>
-      <c r="G16" t="n">
-        <v>148.6667</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>杉创智至</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>59.4667</v>
-      </c>
-      <c r="F17" t="n">
-        <v>59.4667</v>
-      </c>
-      <c r="G17" t="n">
-        <v>59.4667</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>杉晖创业</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="F18" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="G18" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>杭州达晨创程</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>51.959</v>
-      </c>
-      <c r="F19" t="n">
-        <v>51.959</v>
-      </c>
-      <c r="G19" t="n">
-        <v>51.959</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>泽升贸易</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>8976</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>8976</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8976</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>深圳达晨创程</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>86.5984</v>
-      </c>
-      <c r="F21" t="n">
-        <v>86.5984</v>
-      </c>
-      <c r="G21" t="n">
-        <v>86.5984</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>204</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>204</v>
-      </c>
-      <c r="G22" t="n">
-        <v>204</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>财投晨源</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="G23" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>财智创赢</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>10.1093</v>
-      </c>
-      <c r="F24" t="n">
-        <v>10.1093</v>
-      </c>
-      <c r="G24" t="n">
-        <v>10.1093</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>达晨创联基金</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>达晨财智</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="F26" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="G26" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>达晨财汇</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="F27" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="G27" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>金浦临港基金</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>840</v>
-      </c>
-      <c r="E28" t="n">
-        <v>840</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1680</v>
-      </c>
-      <c r="G28" t="n">
-        <v>840</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-840</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>金浦科创基金</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>360</v>
-      </c>
-      <c r="E29" t="n">
-        <v>360</v>
-      </c>
-      <c r="F29" t="n">
-        <v>720</v>
-      </c>
-      <c r="G29" t="n">
-        <v>360</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-360</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,7 +912,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>10950.2788</v>
       </c>
@@ -920,7 +920,6 @@
           <t>泽升贸易</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>8190.8086</v>
       </c>
@@ -949,7 +948,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>10950.2788</v>
       </c>
@@ -958,7 +956,6 @@
           <t>达晨创联基金</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1642.5418</v>
       </c>
@@ -987,7 +984,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>10950.2788</v>
       </c>
@@ -996,7 +992,6 @@
           <t>共青城泽升</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>930.7737</v>
       </c>
@@ -1025,7 +1020,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>10950.2788</v>
       </c>
@@ -1034,7 +1028,6 @@
           <t>罗世兵</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>186.1547</v>
       </c>
@@ -1066,7 +1059,6 @@
       <c r="D6" t="n">
         <v>13380</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1075,7 +1067,6 @@
       <c r="G6" t="n">
         <v>8976</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>67.09%</t>
@@ -1104,7 +1095,6 @@
       <c r="D7" t="n">
         <v>13380</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1113,7 +1103,6 @@
       <c r="G7" t="n">
         <v>1800</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>13.45%</t>
@@ -1142,7 +1131,6 @@
       <c r="D8" t="n">
         <v>13380</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1151,7 +1139,6 @@
       <c r="G8" t="n">
         <v>1020</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>7.62%</t>
@@ -1180,7 +1167,6 @@
       <c r="D9" t="n">
         <v>13380</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1189,7 +1175,6 @@
       <c r="G9" t="n">
         <v>204</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>1.52%</t>
@@ -1218,7 +1203,6 @@
       <c r="D10" t="n">
         <v>13380</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1227,7 +1211,6 @@
       <c r="G10" t="n">
         <v>840</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>6.28%</t>
@@ -1256,7 +1239,6 @@
       <c r="D11" t="n">
         <v>13380</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1265,7 +1247,6 @@
       <c r="G11" t="n">
         <v>360</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2.69%</t>
@@ -1294,7 +1275,6 @@
       <c r="D12" t="n">
         <v>13380</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1303,7 +1283,6 @@
       <c r="G12" t="n">
         <v>180</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>1.35%</t>
@@ -1332,7 +1311,6 @@
       <c r="D13" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1341,7 +1319,6 @@
       <c r="G13" t="n">
         <v>8976</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>61.99%</t>
@@ -1370,7 +1347,6 @@
       <c r="D14" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1379,7 +1355,6 @@
       <c r="G14" t="n">
         <v>1800</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>12.43%</t>
@@ -1408,7 +1383,6 @@
       <c r="D15" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1417,7 +1391,6 @@
       <c r="G15" t="n">
         <v>1020</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>7.04%</t>
@@ -1446,7 +1419,6 @@
       <c r="D16" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1455,7 +1427,6 @@
       <c r="G16" t="n">
         <v>840</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>5.80%</t>
@@ -1484,7 +1455,6 @@
       <c r="D17" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1493,7 +1463,6 @@
       <c r="G17" t="n">
         <v>360</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2.49%</t>
@@ -1522,7 +1491,6 @@
       <c r="D18" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1531,7 +1499,6 @@
       <c r="G18" t="n">
         <v>204</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>1.41%</t>
@@ -1560,7 +1527,6 @@
       <c r="D19" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1569,7 +1535,6 @@
       <c r="G19" t="n">
         <v>180</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>1.24%</t>
@@ -1598,7 +1563,6 @@
       <c r="D20" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>杉晖创业</t>
@@ -1607,7 +1571,6 @@
       <c r="G20" t="n">
         <v>297.3333</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1636,7 +1599,6 @@
       <c r="D21" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>上海联炻</t>
@@ -1645,7 +1607,6 @@
       <c r="G21" t="n">
         <v>297.3333</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1674,7 +1635,6 @@
       <c r="D22" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>安吉璞颉</t>
@@ -1683,7 +1643,6 @@
       <c r="G22" t="n">
         <v>148.6667</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>1.03%</t>
@@ -1712,7 +1671,6 @@
       <c r="D23" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>财投晨源</t>
@@ -1721,7 +1679,6 @@
       <c r="G23" t="n">
         <v>89.2</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>0.62%</t>
@@ -1750,7 +1707,6 @@
       <c r="D24" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>深圳达晨创程</t>
@@ -1759,7 +1715,6 @@
       <c r="G24" t="n">
         <v>86.5984</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>0.60%</t>
@@ -1788,7 +1743,6 @@
       <c r="D25" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>杉创智至</t>
@@ -1797,7 +1751,6 @@
       <c r="G25" t="n">
         <v>59.4667</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>0.41%</t>
@@ -1826,7 +1779,6 @@
       <c r="D26" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>杭州达晨创程</t>
@@ -1835,7 +1787,6 @@
       <c r="G26" t="n">
         <v>51.959</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>0.36%</t>
@@ -1864,7 +1815,6 @@
       <c r="D27" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>达晨财汇</t>
@@ -1873,7 +1823,6 @@
       <c r="G27" t="n">
         <v>29.7333</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1902,7 +1851,6 @@
       <c r="D28" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>达晨财智</t>
@@ -1911,7 +1859,6 @@
       <c r="G28" t="n">
         <v>29.7333</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1940,7 +1887,6 @@
       <c r="D29" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>财智创赢</t>
@@ -1949,7 +1895,6 @@
       <c r="G29" t="n">
         <v>10.1093</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>0.07%</t>
@@ -1960,6 +1905,306 @@
           <t>本次增资后股权结构如下</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴13条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量28条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>10950.2788</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2480.1333</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13430.4121</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13380</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-50.4121</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>13380</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2480.1333</v>
+      </c>
+      <c r="H5" t="n">
+        <v>15860.1333</v>
+      </c>
+      <c r="I5" t="n">
+        <v>14480.1333</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1380</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t0｜报告期初</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4股东</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>比例合计100.00%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7股东</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>比例合计100.00%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>13380</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>17股东</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>比例合计100.01%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>14480.13</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -912,6 +911,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>10950.2788</v>
       </c>
@@ -920,6 +920,7 @@
           <t>泽升贸易</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>8190.8086</v>
       </c>
@@ -948,6 +949,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>10950.2788</v>
       </c>
@@ -956,6 +958,7 @@
           <t>达晨创联基金</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1642.5418</v>
       </c>
@@ -984,6 +987,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>10950.2788</v>
       </c>
@@ -992,6 +996,7 @@
           <t>共青城泽升</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>930.7737</v>
       </c>
@@ -1020,6 +1025,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>10950.2788</v>
       </c>
@@ -1028,6 +1034,7 @@
           <t>罗世兵</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>186.1547</v>
       </c>
@@ -1059,6 +1066,7 @@
       <c r="D6" t="n">
         <v>13380</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1067,6 +1075,7 @@
       <c r="G6" t="n">
         <v>8976</v>
       </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>67.09%</t>
@@ -1095,6 +1104,7 @@
       <c r="D7" t="n">
         <v>13380</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1103,6 +1113,7 @@
       <c r="G7" t="n">
         <v>1800</v>
       </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>13.45%</t>
@@ -1131,6 +1142,7 @@
       <c r="D8" t="n">
         <v>13380</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1139,6 +1151,7 @@
       <c r="G8" t="n">
         <v>1020</v>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>7.62%</t>
@@ -1167,6 +1180,7 @@
       <c r="D9" t="n">
         <v>13380</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1175,6 +1189,7 @@
       <c r="G9" t="n">
         <v>204</v>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>1.52%</t>
@@ -1203,6 +1218,7 @@
       <c r="D10" t="n">
         <v>13380</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1211,6 +1227,7 @@
       <c r="G10" t="n">
         <v>840</v>
       </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>6.28%</t>
@@ -1239,6 +1256,7 @@
       <c r="D11" t="n">
         <v>13380</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1247,6 +1265,7 @@
       <c r="G11" t="n">
         <v>360</v>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2.69%</t>
@@ -1275,6 +1294,7 @@
       <c r="D12" t="n">
         <v>13380</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1283,6 +1303,7 @@
       <c r="G12" t="n">
         <v>180</v>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>1.35%</t>
@@ -1311,6 +1332,7 @@
       <c r="D13" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1319,6 +1341,7 @@
       <c r="G13" t="n">
         <v>8976</v>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>61.99%</t>
@@ -1347,6 +1370,7 @@
       <c r="D14" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1355,6 +1379,7 @@
       <c r="G14" t="n">
         <v>1800</v>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>12.43%</t>
@@ -1383,6 +1408,7 @@
       <c r="D15" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1391,6 +1417,7 @@
       <c r="G15" t="n">
         <v>1020</v>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>7.04%</t>
@@ -1419,6 +1446,7 @@
       <c r="D16" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1427,6 +1455,7 @@
       <c r="G16" t="n">
         <v>840</v>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>5.80%</t>
@@ -1455,6 +1484,7 @@
       <c r="D17" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1463,6 +1493,7 @@
       <c r="G17" t="n">
         <v>360</v>
       </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2.49%</t>
@@ -1491,6 +1522,7 @@
       <c r="D18" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1499,6 +1531,7 @@
       <c r="G18" t="n">
         <v>204</v>
       </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>1.41%</t>
@@ -1527,6 +1560,7 @@
       <c r="D19" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1535,6 +1569,7 @@
       <c r="G19" t="n">
         <v>180</v>
       </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>1.24%</t>
@@ -1563,6 +1598,7 @@
       <c r="D20" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>杉晖创业</t>
@@ -1571,6 +1607,7 @@
       <c r="G20" t="n">
         <v>297.3333</v>
       </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1599,6 +1636,7 @@
       <c r="D21" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>上海联炻</t>
@@ -1607,6 +1645,7 @@
       <c r="G21" t="n">
         <v>297.3333</v>
       </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1635,6 +1674,7 @@
       <c r="D22" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>安吉璞颉</t>
@@ -1643,6 +1683,7 @@
       <c r="G22" t="n">
         <v>148.6667</v>
       </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>1.03%</t>
@@ -1671,6 +1712,7 @@
       <c r="D23" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>财投晨源</t>
@@ -1679,6 +1721,7 @@
       <c r="G23" t="n">
         <v>89.2</v>
       </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>0.62%</t>
@@ -1707,6 +1750,7 @@
       <c r="D24" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>深圳达晨创程</t>
@@ -1715,6 +1759,7 @@
       <c r="G24" t="n">
         <v>86.5984</v>
       </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>0.60%</t>
@@ -1743,6 +1788,7 @@
       <c r="D25" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>杉创智至</t>
@@ -1751,6 +1797,7 @@
       <c r="G25" t="n">
         <v>59.4667</v>
       </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>0.41%</t>
@@ -1779,6 +1826,7 @@
       <c r="D26" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>杭州达晨创程</t>
@@ -1787,6 +1835,7 @@
       <c r="G26" t="n">
         <v>51.959</v>
       </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>0.36%</t>
@@ -1815,6 +1864,7 @@
       <c r="D27" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>达晨财汇</t>
@@ -1823,6 +1873,7 @@
       <c r="G27" t="n">
         <v>29.7333</v>
       </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1851,6 +1902,7 @@
       <c r="D28" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>达晨财智</t>
@@ -1859,6 +1911,7 @@
       <c r="G28" t="n">
         <v>29.7333</v>
       </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1887,6 +1940,7 @@
       <c r="D29" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>财智创赢</t>
@@ -1895,6 +1949,7 @@
       <c r="G29" t="n">
         <v>10.1093</v>
       </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>0.07%</t>
@@ -1905,306 +1960,6 @@
           <t>本次增资后股权结构如下</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴13条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量28条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>10950.2788</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2480.1333</v>
-      </c>
-      <c r="H4" t="n">
-        <v>13430.4121</v>
-      </c>
-      <c r="I4" t="n">
-        <v>13380</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-50.4121</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>13380</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2480.1333</v>
-      </c>
-      <c r="H5" t="n">
-        <v>15860.1333</v>
-      </c>
-      <c r="I5" t="n">
-        <v>14480.1333</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-1380</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t0｜报告期初</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4股东</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>比例合计100.00%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>7股东</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>比例合计100.00%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
-        <v>13380</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>17股东</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>比例合计100.01%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
-        <v>14480.13</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,7 +912,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>10950.2788</v>
       </c>
@@ -920,7 +920,6 @@
           <t>泽升贸易</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>8190.8086</v>
       </c>
@@ -949,7 +948,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>10950.2788</v>
       </c>
@@ -958,7 +956,6 @@
           <t>达晨创联基金</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1642.5418</v>
       </c>
@@ -987,7 +984,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>10950.2788</v>
       </c>
@@ -996,7 +992,6 @@
           <t>共青城泽升</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>930.7737</v>
       </c>
@@ -1025,7 +1020,6 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>10950.2788</v>
       </c>
@@ -1034,7 +1028,6 @@
           <t>罗世兵</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>186.1547</v>
       </c>
@@ -1066,7 +1059,6 @@
       <c r="D6" t="n">
         <v>13380</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1075,7 +1067,6 @@
       <c r="G6" t="n">
         <v>8976</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>67.09%</t>
@@ -1104,7 +1095,6 @@
       <c r="D7" t="n">
         <v>13380</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1113,7 +1103,6 @@
       <c r="G7" t="n">
         <v>1800</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>13.45%</t>
@@ -1142,7 +1131,6 @@
       <c r="D8" t="n">
         <v>13380</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1151,7 +1139,6 @@
       <c r="G8" t="n">
         <v>1020</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>7.62%</t>
@@ -1180,7 +1167,6 @@
       <c r="D9" t="n">
         <v>13380</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1189,7 +1175,6 @@
       <c r="G9" t="n">
         <v>204</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>1.52%</t>
@@ -1218,7 +1203,6 @@
       <c r="D10" t="n">
         <v>13380</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1227,7 +1211,6 @@
       <c r="G10" t="n">
         <v>840</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>6.28%</t>
@@ -1256,7 +1239,6 @@
       <c r="D11" t="n">
         <v>13380</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1265,7 +1247,6 @@
       <c r="G11" t="n">
         <v>360</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2.69%</t>
@@ -1294,7 +1275,6 @@
       <c r="D12" t="n">
         <v>13380</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1303,7 +1283,6 @@
       <c r="G12" t="n">
         <v>180</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>1.35%</t>
@@ -1332,7 +1311,6 @@
       <c r="D13" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1341,7 +1319,6 @@
       <c r="G13" t="n">
         <v>8976</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>61.99%</t>
@@ -1370,7 +1347,6 @@
       <c r="D14" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1379,7 +1355,6 @@
       <c r="G14" t="n">
         <v>1800</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>12.43%</t>
@@ -1408,7 +1383,6 @@
       <c r="D15" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1417,7 +1391,6 @@
       <c r="G15" t="n">
         <v>1020</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>7.04%</t>
@@ -1446,7 +1419,6 @@
       <c r="D16" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1455,7 +1427,6 @@
       <c r="G16" t="n">
         <v>840</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>5.80%</t>
@@ -1484,7 +1455,6 @@
       <c r="D17" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1493,7 +1463,6 @@
       <c r="G17" t="n">
         <v>360</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2.49%</t>
@@ -1522,7 +1491,6 @@
       <c r="D18" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1531,7 +1499,6 @@
       <c r="G18" t="n">
         <v>204</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>1.41%</t>
@@ -1560,7 +1527,6 @@
       <c r="D19" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1569,7 +1535,6 @@
       <c r="G19" t="n">
         <v>180</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>1.24%</t>
@@ -1598,7 +1563,6 @@
       <c r="D20" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>杉晖创业</t>
@@ -1607,7 +1571,6 @@
       <c r="G20" t="n">
         <v>297.3333</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1636,7 +1599,6 @@
       <c r="D21" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>上海联炻</t>
@@ -1645,7 +1607,6 @@
       <c r="G21" t="n">
         <v>297.3333</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1674,7 +1635,6 @@
       <c r="D22" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>安吉璞颉</t>
@@ -1683,7 +1643,6 @@
       <c r="G22" t="n">
         <v>148.6667</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>1.03%</t>
@@ -1712,7 +1671,6 @@
       <c r="D23" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>财投晨源</t>
@@ -1721,7 +1679,6 @@
       <c r="G23" t="n">
         <v>89.2</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>0.62%</t>
@@ -1750,7 +1707,6 @@
       <c r="D24" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>深圳达晨创程</t>
@@ -1759,7 +1715,6 @@
       <c r="G24" t="n">
         <v>86.5984</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>0.60%</t>
@@ -1788,7 +1743,6 @@
       <c r="D25" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>杉创智至</t>
@@ -1797,7 +1751,6 @@
       <c r="G25" t="n">
         <v>59.4667</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>0.41%</t>
@@ -1826,7 +1779,6 @@
       <c r="D26" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>杭州达晨创程</t>
@@ -1835,7 +1787,6 @@
       <c r="G26" t="n">
         <v>51.959</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>0.36%</t>
@@ -1864,7 +1815,6 @@
       <c r="D27" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>达晨财汇</t>
@@ -1873,7 +1823,6 @@
       <c r="G27" t="n">
         <v>29.7333</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1902,7 +1851,6 @@
       <c r="D28" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>达晨财智</t>
@@ -1911,7 +1859,6 @@
       <c r="G28" t="n">
         <v>29.7333</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1940,7 +1887,6 @@
       <c r="D29" t="n">
         <v>14480.1333</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>财智创赢</t>
@@ -1949,7 +1895,6 @@
       <c r="G29" t="n">
         <v>10.1093</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>0.07%</t>
@@ -1958,6 +1903,197 @@
       <c r="J29" t="inlineStr">
         <is>
           <t>本次增资后股权结构如下</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴13条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量28条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>转让5条</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>已合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t0｜报告期初</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4股东</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>比例合计100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7股东</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>比例合计100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>17股东</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>比例合计100.01%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -1917,7 +1917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1928,20 +1928,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>时点</t>
+          <t>PDF页码</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>股东</t>
+          <t>股东/认购方</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化(万股)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值(万股)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额(万股)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>校验结果</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1956,17 +1981,22 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>认缴13条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>认缴流量</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段完整</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13条,字段完整</t>
         </is>
       </c>
     </row>
@@ -1979,121 +2009,1094 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>存量28条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>股权存量</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>28条,t0存在</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>schema</t>
+          <t>cross_check_total</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>转让5条</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>已合并</t>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2480.1333</v>
+      </c>
+      <c r="F4" t="n">
+        <v>14480.1333</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13380</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1100.1333</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t0｜报告期初</t>
-        </is>
-      </c>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4股东</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>比例合计100.00%</t>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13380</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2480.1333</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15860.1333</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14480.1333</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-1380</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后</t>
-        </is>
-      </c>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7股东</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>上海骁墨</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>180</v>
+      </c>
+      <c r="F6" t="n">
+        <v>180</v>
+      </c>
+      <c r="G6" t="n">
+        <v>180</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>比例合计100.00%</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>共青城泽升</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1020</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>泽升贸易</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8976</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8976</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8976</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>204</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>204</v>
+      </c>
+      <c r="G9" t="n">
+        <v>204</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>达晨创联基金</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>金浦临港基金</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>840</v>
+      </c>
+      <c r="F11" t="n">
+        <v>840</v>
+      </c>
+      <c r="G11" t="n">
+        <v>840</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>金浦科创基金</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>360</v>
+      </c>
+      <c r="F12" t="n">
+        <v>360</v>
+      </c>
+      <c r="G12" t="n">
+        <v>360</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>上海联炻</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="F13" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="G13" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上海骁墨</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>180</v>
+      </c>
+      <c r="E14" t="n">
+        <v>180</v>
+      </c>
+      <c r="F14" t="n">
+        <v>360</v>
+      </c>
+      <c r="G14" t="n">
+        <v>180</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-180</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>共青城泽升</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1020</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>安吉璞颉</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>148.6667</v>
+      </c>
+      <c r="F16" t="n">
+        <v>148.6667</v>
+      </c>
+      <c r="G16" t="n">
+        <v>148.6667</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>杉创智至</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>59.4667</v>
+      </c>
+      <c r="F17" t="n">
+        <v>59.4667</v>
+      </c>
+      <c r="G17" t="n">
+        <v>59.4667</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>杉晖创业</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="F18" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="G18" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>杭州达晨创程</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>51.959</v>
+      </c>
+      <c r="F19" t="n">
+        <v>51.959</v>
+      </c>
+      <c r="G19" t="n">
+        <v>51.959</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>泽升贸易</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>8976</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8976</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8976</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>深圳达晨创程</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>86.5984</v>
+      </c>
+      <c r="F21" t="n">
+        <v>86.5984</v>
+      </c>
+      <c r="G21" t="n">
+        <v>86.5984</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>204</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>204</v>
+      </c>
+      <c r="G22" t="n">
+        <v>204</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>财投晨源</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>财智创赢</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10.1093</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10.1093</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10.1093</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>达晨创联基金</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>达晨财智</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="F26" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="G26" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>达晨财汇</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="F27" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="G27" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>金浦临港基金</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>840</v>
+      </c>
+      <c r="E28" t="n">
+        <v>840</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1680</v>
+      </c>
+      <c r="G28" t="n">
+        <v>840</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-840</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>金浦科创基金</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>360</v>
+      </c>
+      <c r="E29" t="n">
+        <v>360</v>
+      </c>
+      <c r="F29" t="n">
+        <v>720</v>
+      </c>
+      <c r="G29" t="n">
+        <v>360</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-360</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>ratio_check</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4股东</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>t0｜报告期初比例合计100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7股东</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>t1｜2020-09-30增资后比例合计100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
         <is>
           <t>17股东</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>比例合计100.01%</t>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>t2｜2022-12-19增资后比例合计100.01%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -912,6 +911,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>10950.2788</v>
       </c>
@@ -919,6 +919,9 @@
         <is>
           <t>泽升贸易</t>
         </is>
+      </c>
+      <c r="G2" t="n">
+        <v>8976</v>
       </c>
       <c r="H2" t="n">
         <v>8190.8086</v>
@@ -948,6 +951,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>10950.2788</v>
       </c>
@@ -955,6 +959,9 @@
         <is>
           <t>达晨创联基金</t>
         </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1800</v>
       </c>
       <c r="H3" t="n">
         <v>1642.5418</v>
@@ -984,6 +991,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>10950.2788</v>
       </c>
@@ -991,6 +999,9 @@
         <is>
           <t>共青城泽升</t>
         </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1020</v>
       </c>
       <c r="H4" t="n">
         <v>930.7737</v>
@@ -1020,6 +1031,7 @@
           <t>报告期初公司的股权结构</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>10950.2788</v>
       </c>
@@ -1027,6 +1039,9 @@
         <is>
           <t>罗世兵</t>
         </is>
+      </c>
+      <c r="G5" t="n">
+        <v>204</v>
       </c>
       <c r="H5" t="n">
         <v>186.1547</v>
@@ -1059,6 +1074,7 @@
       <c r="D6" t="n">
         <v>13380</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1066,6 +1082,9 @@
       </c>
       <c r="G6" t="n">
         <v>8976</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8190.8086</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1095,6 +1114,7 @@
       <c r="D7" t="n">
         <v>13380</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1102,6 +1122,9 @@
       </c>
       <c r="G7" t="n">
         <v>1800</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1642.5418</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1131,6 +1154,7 @@
       <c r="D8" t="n">
         <v>13380</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1138,6 +1162,9 @@
       </c>
       <c r="G8" t="n">
         <v>1020</v>
+      </c>
+      <c r="H8" t="n">
+        <v>930.7737</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1167,6 +1194,7 @@
       <c r="D9" t="n">
         <v>13380</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1174,6 +1202,9 @@
       </c>
       <c r="G9" t="n">
         <v>204</v>
+      </c>
+      <c r="H9" t="n">
+        <v>186.1547</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1203,6 +1234,7 @@
       <c r="D10" t="n">
         <v>13380</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1211,6 +1243,7 @@
       <c r="G10" t="n">
         <v>840</v>
       </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>6.28%</t>
@@ -1239,6 +1272,7 @@
       <c r="D11" t="n">
         <v>13380</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1247,6 +1281,7 @@
       <c r="G11" t="n">
         <v>360</v>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2.69%</t>
@@ -1275,6 +1310,7 @@
       <c r="D12" t="n">
         <v>13380</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1283,6 +1319,7 @@
       <c r="G12" t="n">
         <v>180</v>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>1.35%</t>
@@ -1311,6 +1348,7 @@
       <c r="D13" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>泽升贸易</t>
@@ -1319,6 +1357,9 @@
       <c r="G13" t="n">
         <v>8976</v>
       </c>
+      <c r="H13" t="n">
+        <v>8190.8086</v>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>61.99%</t>
@@ -1347,6 +1388,7 @@
       <c r="D14" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>达晨创联基金</t>
@@ -1355,6 +1397,9 @@
       <c r="G14" t="n">
         <v>1800</v>
       </c>
+      <c r="H14" t="n">
+        <v>1642.5418</v>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>12.43%</t>
@@ -1383,6 +1428,7 @@
       <c r="D15" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>共青城泽升</t>
@@ -1391,6 +1437,9 @@
       <c r="G15" t="n">
         <v>1020</v>
       </c>
+      <c r="H15" t="n">
+        <v>930.7737</v>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>7.04%</t>
@@ -1419,6 +1468,7 @@
       <c r="D16" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
@@ -1427,6 +1477,7 @@
       <c r="G16" t="n">
         <v>840</v>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>5.80%</t>
@@ -1455,6 +1506,7 @@
       <c r="D17" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
@@ -1463,6 +1515,7 @@
       <c r="G17" t="n">
         <v>360</v>
       </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2.49%</t>
@@ -1491,6 +1544,7 @@
       <c r="D18" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>罗世兵</t>
@@ -1499,6 +1553,9 @@
       <c r="G18" t="n">
         <v>204</v>
       </c>
+      <c r="H18" t="n">
+        <v>186.1547</v>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>1.41%</t>
@@ -1527,6 +1584,7 @@
       <c r="D19" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>上海骁墨</t>
@@ -1535,6 +1593,7 @@
       <c r="G19" t="n">
         <v>180</v>
       </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>1.24%</t>
@@ -1563,6 +1622,7 @@
       <c r="D20" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>杉晖创业</t>
@@ -1571,6 +1631,7 @@
       <c r="G20" t="n">
         <v>297.3333</v>
       </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1599,6 +1660,7 @@
       <c r="D21" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>上海联炻</t>
@@ -1607,6 +1669,7 @@
       <c r="G21" t="n">
         <v>297.3333</v>
       </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>2.05%</t>
@@ -1635,6 +1698,7 @@
       <c r="D22" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>安吉璞颉</t>
@@ -1643,6 +1707,7 @@
       <c r="G22" t="n">
         <v>148.6667</v>
       </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>1.03%</t>
@@ -1671,6 +1736,7 @@
       <c r="D23" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>财投晨源</t>
@@ -1679,6 +1745,7 @@
       <c r="G23" t="n">
         <v>89.2</v>
       </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>0.62%</t>
@@ -1707,6 +1774,7 @@
       <c r="D24" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>深圳达晨创程</t>
@@ -1715,6 +1783,7 @@
       <c r="G24" t="n">
         <v>86.5984</v>
       </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>0.60%</t>
@@ -1743,6 +1812,7 @@
       <c r="D25" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>杉创智至</t>
@@ -1751,6 +1821,7 @@
       <c r="G25" t="n">
         <v>59.4667</v>
       </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>0.41%</t>
@@ -1779,6 +1850,7 @@
       <c r="D26" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>杭州达晨创程</t>
@@ -1787,6 +1859,7 @@
       <c r="G26" t="n">
         <v>51.959</v>
       </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>0.36%</t>
@@ -1815,6 +1888,7 @@
       <c r="D27" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>达晨财汇</t>
@@ -1823,6 +1897,7 @@
       <c r="G27" t="n">
         <v>29.7333</v>
       </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1851,6 +1926,7 @@
       <c r="D28" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>达晨财智</t>
@@ -1859,6 +1935,7 @@
       <c r="G28" t="n">
         <v>29.7333</v>
       </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>0.21%</t>
@@ -1887,6 +1964,7 @@
       <c r="D29" t="n">
         <v>14480.1333</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>财智创赢</t>
@@ -1895,6 +1973,7 @@
       <c r="G29" t="n">
         <v>10.1093</v>
       </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>0.07%</t>
@@ -1903,1200 +1982,6 @@
       <c r="J29" t="inlineStr">
         <is>
           <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>PDF页码</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东/认购方</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化(万股)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值(万股)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额(万股)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴流量</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>13条,字段完整</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>股权存量</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>28条,t0存在</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2480.1333</v>
-      </c>
-      <c r="F4" t="n">
-        <v>14480.1333</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13380</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-1100.1333</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>13380</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2480.1333</v>
-      </c>
-      <c r="F5" t="n">
-        <v>15860.1333</v>
-      </c>
-      <c r="G5" t="n">
-        <v>14480.1333</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-1380</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>上海骁墨</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>180</v>
-      </c>
-      <c r="F6" t="n">
-        <v>180</v>
-      </c>
-      <c r="G6" t="n">
-        <v>180</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>共青城泽升</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1020</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1020</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>泽升贸易</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>8976</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8976</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8976</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>204</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>204</v>
-      </c>
-      <c r="G9" t="n">
-        <v>204</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>达晨创联基金</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>金浦临港基金</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>840</v>
-      </c>
-      <c r="F11" t="n">
-        <v>840</v>
-      </c>
-      <c r="G11" t="n">
-        <v>840</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>金浦科创基金</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>360</v>
-      </c>
-      <c r="F12" t="n">
-        <v>360</v>
-      </c>
-      <c r="G12" t="n">
-        <v>360</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>t0｜报告期初-&gt;t1｜2020-09-30增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>上海联炻</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="F13" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="G13" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>上海骁墨</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>180</v>
-      </c>
-      <c r="E14" t="n">
-        <v>180</v>
-      </c>
-      <c r="F14" t="n">
-        <v>360</v>
-      </c>
-      <c r="G14" t="n">
-        <v>180</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-180</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>共青城泽升</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1020</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1020</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>安吉璞颉</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>148.6667</v>
-      </c>
-      <c r="F16" t="n">
-        <v>148.6667</v>
-      </c>
-      <c r="G16" t="n">
-        <v>148.6667</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>杉创智至</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>59.4667</v>
-      </c>
-      <c r="F17" t="n">
-        <v>59.4667</v>
-      </c>
-      <c r="G17" t="n">
-        <v>59.4667</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>杉晖创业</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="F18" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="G18" t="n">
-        <v>297.3333</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>杭州达晨创程</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>51.959</v>
-      </c>
-      <c r="F19" t="n">
-        <v>51.959</v>
-      </c>
-      <c r="G19" t="n">
-        <v>51.959</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>泽升贸易</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>8976</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>8976</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8976</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>深圳达晨创程</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>86.5984</v>
-      </c>
-      <c r="F21" t="n">
-        <v>86.5984</v>
-      </c>
-      <c r="G21" t="n">
-        <v>86.5984</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>204</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>204</v>
-      </c>
-      <c r="G22" t="n">
-        <v>204</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>财投晨源</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="G23" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>财智创赢</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>10.1093</v>
-      </c>
-      <c r="F24" t="n">
-        <v>10.1093</v>
-      </c>
-      <c r="G24" t="n">
-        <v>10.1093</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>达晨创联基金</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>达晨财智</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="F26" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="G26" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>达晨财汇</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="F27" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="G27" t="n">
-        <v>29.7333</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>金浦临港基金</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>840</v>
-      </c>
-      <c r="E28" t="n">
-        <v>840</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1680</v>
-      </c>
-      <c r="G28" t="n">
-        <v>840</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-840</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>金浦科创基金</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>360</v>
-      </c>
-      <c r="E29" t="n">
-        <v>360</v>
-      </c>
-      <c r="F29" t="n">
-        <v>720</v>
-      </c>
-      <c r="G29" t="n">
-        <v>360</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-360</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后-&gt;t2｜2022-12-19增资后</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>4股东</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>t0｜报告期初比例合计100.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>7股东</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>t1｜2020-09-30增资后比例合计100.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>17股东</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>t2｜2022-12-19增资后比例合计100.01%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>金浦临港基金以7000万元认购新增注册资本840万元</t>
+          <t>金浦临港基金以7000万元认购新增注册资本840万元 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>金浦科创基金以3000万元认购新增注册资本360万元</t>
+          <t>金浦科创基金以3000万元认购新增注册资本360万元 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>上海骁墨以1500万元认购新增注册资本180万元</t>
+          <t>上海骁墨以1500万元认购新增注册资本180万元 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>杉晖创业认购297.3333万股且认购金额10000万元</t>
+          <t>杉晖创业认购297.3333万股且认购金额10000万元 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>上海联炻认购297.3333万股且认购金额10000万元</t>
+          <t>上海联炻认购297.3333万股且认购金额10000万元 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>安吉璞颉认购148.6667万股且认购金额5000万元</t>
+          <t>安吉璞颉认购148.6667万股且认购金额5000万元 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>财投晨源认购89.2000万股且认购金额3000万元</t>
+          <t>财投晨源认购89.2000万股且认购金额3000万元 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>深圳达晨创程认购86.5984万股且认购金额2912.50万元</t>
+          <t>深圳达晨创程认购86.5984万股且认购金额2912.50万元 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>杉创智至认购59.4667万股且认购金额2000万元</t>
+          <t>杉创智至认购59.4667万股且认购金额2000万元 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>杭州达晨创程认购51.9590万股且认购金额1747.50万元</t>
+          <t>杭州达晨创程认购51.9590万股且认购金额1747.50万元 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>达晨财汇认购29.7333万股且认购金额1000万元</t>
+          <t>达晨财汇认购29.7333万股且认购金额1000万元 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>达晨财智认购29.7333万股且认购金额1000万元</t>
+          <t>达晨财智认购29.7333万股且认购金额1000万元 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>财智创赢认购10.1093万股且认购金额340万元</t>
+          <t>财智创赢认购10.1093万股且认购金额340万元 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>报告期初公司的股权结构</t>
+          <t>报告期初公司的股权结构 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>报告期初公司的股权结构</t>
+          <t>报告期初公司的股权结构 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>报告期初公司的股权结构</t>
+          <t>报告期初公司的股权结构 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>报告期初公司的股权结构</t>
+          <t>报告期初公司的股权结构 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
+          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>金浦临港基金以7000万元认购新增注册资本840万元 [教师Gold, PDF原文已核对]</t>
+          <t>金浦临港基金以7000万元认购新增注册资本840万元</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>金浦科创基金以3000万元认购新增注册资本360万元 [教师Gold, PDF原文已核对]</t>
+          <t>金浦科创基金以3000万元认购新增注册资本360万元</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>上海骁墨以1500万元认购新增注册资本180万元 [教师Gold, PDF原文已核对]</t>
+          <t>上海骁墨以1500万元认购新增注册资本180万元</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>杉晖创业认购297.3333万股且认购金额10000万元 [教师Gold, PDF原文已核对]</t>
+          <t>杉晖创业认购297.3333万股且认购金额10000万元</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>上海联炻认购297.3333万股且认购金额10000万元 [教师Gold, PDF原文已核对]</t>
+          <t>上海联炻认购297.3333万股且认购金额10000万元</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>安吉璞颉认购148.6667万股且认购金额5000万元 [教师Gold, PDF原文已核对]</t>
+          <t>安吉璞颉认购148.6667万股且认购金额5000万元</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>财投晨源认购89.2000万股且认购金额3000万元 [教师Gold, PDF原文已核对]</t>
+          <t>财投晨源认购89.2000万股且认购金额3000万元</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>深圳达晨创程认购86.5984万股且认购金额2912.50万元 [教师Gold, PDF原文已核对]</t>
+          <t>深圳达晨创程认购86.5984万股且认购金额2912.50万元</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>杉创智至认购59.4667万股且认购金额2000万元 [教师Gold, PDF原文已核对]</t>
+          <t>杉创智至认购59.4667万股且认购金额2000万元</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>杭州达晨创程认购51.9590万股且认购金额1747.50万元 [教师Gold, PDF原文已核对]</t>
+          <t>杭州达晨创程认购51.9590万股且认购金额1747.50万元</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>达晨财汇认购29.7333万股且认购金额1000万元 [教师Gold, PDF原文已核对]</t>
+          <t>达晨财汇认购29.7333万股且认购金额1000万元</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>达晨财智认购29.7333万股且认购金额1000万元 [教师Gold, PDF原文已核对]</t>
+          <t>达晨财智认购29.7333万股且认购金额1000万元</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>财智创赢认购10.1093万股且认购金额340万元 [教师Gold, PDF原文已核对]</t>
+          <t>财智创赢认购10.1093万股且认购金额340万元</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,1089 +899,1889 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t0｜报告期初</t>
+          <t>（一）有限责任公司的设立情况 | 设立时</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>报告期初公司的股权结构</t>
+          <t>（一）有限责任公司的设立情况 | 设立时</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>10950.2788</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>泽升贸易</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8976</v>
-      </c>
+          <t>徐泾工业公司</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>8190.8086</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>74.80%</t>
-        </is>
+        <v>240</v>
+      </c>
+      <c r="I2" t="n">
+        <v>60</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>报告期初公司的股权结构 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: （一）有限责任公司的设立情况 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t0｜报告期初</t>
+          <t>（一）有限责任公司的设立情况 | 设立时</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>报告期初公司的股权结构</t>
+          <t>（一）有限责任公司的设立情况 | 设立时</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>10950.2788</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>达晨创联基金</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1800</v>
-      </c>
+          <t>友升太平洋美国</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>1642.5418</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15.00%</t>
-        </is>
+        <v>160</v>
+      </c>
+      <c r="I3" t="n">
+        <v>40</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>报告期初公司的股权结构 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: （一）有限责任公司的设立情况 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t0｜报告期初</t>
+          <t>（二）股份有限公司的设立情况 | 设立时</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>报告期初公司的股权结构</t>
+          <t>（二）股份有限公司的设立情况 | 设立时</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>10950.2788</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>共青城泽升</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1020</v>
-      </c>
-      <c r="H4" t="n">
-        <v>930.7737</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8.50%</t>
-        </is>
+          <t>泽升贸易</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>74.8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>报告期初公司的股权结构 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: （二）股份有限公司的设立情况 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t0｜报告期初</t>
+          <t>（二）股份有限公司的设立情况 | 设立时</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>报告期初公司的股权结构</t>
+          <t>（二）股份有限公司的设立情况 | 设立时</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>10950.2788</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>204</v>
-      </c>
-      <c r="H5" t="n">
-        <v>186.1547</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1.70%</t>
-        </is>
+          <t>达晨创联基金</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>15</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>报告期初公司的股权结构 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: （二）股份有限公司的设立情况 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t1｜2020-09-30增资后</t>
+          <t>（二）股份有限公司的设立情况 | 设立时</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>13380</v>
-      </c>
+          <t>（二）股份有限公司的设立情况 | 设立时</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>泽升贸易</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>8976</v>
-      </c>
-      <c r="H6" t="n">
-        <v>8190.8086</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>67.09%</t>
-        </is>
+          <t>共青城泽升</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>8.5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: （二）股份有限公司的设立情况 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t1｜2020-09-30增资后</t>
+          <t>（二）股份有限公司的设立情况 | 设立时</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>13380</v>
-      </c>
+          <t>（二）股份有限公司的设立情况 | 设立时</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>达晨创联基金</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1642.5418</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>13.45%</t>
-        </is>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>1.7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: （二）股份有限公司的设立情况 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t1｜2020-09-30增资后</t>
+          <t>报告期初 | 设立时</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13380</v>
-      </c>
+          <t>报告期初 | 设立时</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>共青城泽升</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1020</v>
-      </c>
+          <t>泽升贸易</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>930.7737</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7.62%</t>
-        </is>
+        <v>8190.8086</v>
+      </c>
+      <c r="I8" t="n">
+        <v>74.8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t1｜2020-09-30增资后</t>
+          <t>报告期初 | 设立时</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>13380</v>
-      </c>
+          <t>报告期初 | 设立时</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>204</v>
-      </c>
+          <t>达晨创联基金</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>186.1547</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1.52%</t>
-        </is>
+        <v>1642.5418</v>
+      </c>
+      <c r="I9" t="n">
+        <v>15</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>t1｜2020-09-30增资后</t>
+          <t>报告期初 | 设立时</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>13380</v>
-      </c>
+          <t>报告期初 | 设立时</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>金浦临港基金</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>840</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6.28%</t>
-        </is>
+          <t>共青城泽升</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>930.7737</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8.5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t1｜2020-09-30增资后</t>
+          <t>报告期初 | 设立时</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>13380</v>
-      </c>
+          <t>报告期初 | 设立时</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>金浦科创基金</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>360</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.69%</t>
-        </is>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>186.1547</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>t1｜2020-09-30增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>13380</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>上海骁墨</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>180</v>
-      </c>
+          <t>泽升贸易</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1.35%</t>
-        </is>
+      <c r="I12" t="n">
+        <v>67.09</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>泽升贸易</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>8976</v>
-      </c>
-      <c r="H13" t="n">
-        <v>8190.8086</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>61.99%</t>
-        </is>
+          <t>达晨创联基金</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>13.45</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>达晨创联基金</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1642.5418</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12.43%</t>
-        </is>
+          <t>共青城泽升</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>7.62</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>共青城泽升</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>1020</v>
-      </c>
-      <c r="H15" t="n">
-        <v>930.7737</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7.04%</t>
-        </is>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>1.52</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>金浦临港基金</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>840</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5.80%</t>
-        </is>
+      <c r="I16" t="n">
+        <v>6.28</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>金浦科创基金</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>360</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2.49%</t>
-        </is>
+      <c r="I17" t="n">
+        <v>2.69</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>204</v>
-      </c>
-      <c r="H18" t="n">
-        <v>186.1547</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1.41%</t>
-        </is>
+          <t>上海骁墨</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>1.35</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>上海骁墨</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>180</v>
-      </c>
+          <t>泽升贸易</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1.24%</t>
-        </is>
+      <c r="I19" t="n">
+        <v>61.99</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>杉晖创业</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>297.3333</v>
-      </c>
+          <t>达晨创联基金</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2.05%</t>
-        </is>
+      <c r="I20" t="n">
+        <v>12.43</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>上海联炻</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>297.3333</v>
-      </c>
+          <t>共青城泽升</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2.05%</t>
-        </is>
+      <c r="I21" t="n">
+        <v>7.04</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>安吉璞颉</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>148.6667</v>
-      </c>
+          <t>金浦临港基金</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1.03%</t>
-        </is>
+      <c r="I22" t="n">
+        <v>5.8</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>财投晨源</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>89.2</v>
-      </c>
+          <t>金浦科创基金</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.62%</t>
-        </is>
+      <c r="I23" t="n">
+        <v>2.49</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>深圳达晨创程</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>86.5984</v>
-      </c>
+          <t>杉晖创业</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.60%</t>
-        </is>
+      <c r="I24" t="n">
+        <v>2.05</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>杉创智至</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>59.4667</v>
-      </c>
+          <t>上海联炻</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0.41%</t>
-        </is>
+      <c r="I25" t="n">
+        <v>2.05</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>杭州达晨创程</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>51.959</v>
-      </c>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>0.36%</t>
-        </is>
+      <c r="I26" t="n">
+        <v>1.41</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>达晨财汇</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>29.7333</v>
-      </c>
+          <t>上海骁墨</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0.21%</t>
-        </is>
+      <c r="I27" t="n">
+        <v>1.24</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>达晨财智</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>29.7333</v>
-      </c>
+          <t>安吉璞颉</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0.21%</t>
-        </is>
+      <c r="I28" t="n">
+        <v>1.03</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>t2｜2022-12-19增资后</t>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>本次增资后股权结构如下</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>14480.1333</v>
-      </c>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
+          <t>财投晨源</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>深圳达晨创程</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>杉创智至</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>杭州达晨创程</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>达晨财汇</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>0</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>达晨财智</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>增资后，友升股份的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>财智创赢</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>10.1093</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>0.07%</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>本次增资后股权结构如下 [教师Gold, PDF原文已核对]</t>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，友升股份的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>泽升贸易</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>8976</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）发行前后的股本结构 | （二）本次发行前的前十名股东, 比例合计97.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>达晨创联基金</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）发行前后的股本结构 | （二）本次发行前的前十名股东, 比例合计97.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>共青城泽升</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）发行前后的股本结构 | （二）本次发行前的前十名股东, 比例合计97.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>金浦临港基金</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>840</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）发行前后的股本结构 | （二）本次发行前的前十名股东, 比例合计97.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>金浦科创基金</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>360</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）发行前后的股本结构 | （二）本次发行前的前十名股东, 比例合计97.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>杉晖创业</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）发行前后的股本结构 | （二）本次发行前的前十名股东, 比例合计97.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>上海联炻</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）发行前后的股本结构 | （二）本次发行前的前十名股东, 比例合计97.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>0</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>204</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）发行前后的股本结构 | （二）本次发行前的前十名股东, 比例合计97.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>0</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>上海骁墨</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>180</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）发行前后的股本结构 | （二）本次发行前的前十名股东, 比例合计97.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>0</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>（一）发行前后的股本结构 | （二）本次发行前的前十名股东</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>安吉璞颉</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>148.6667</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Markdown表格: （一）发行前后的股本结构 | （二）本次发行前的前十名股东, 比例合计97.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>0</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Markdown表格: （六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例, 比例合计95.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>0</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>泽升贸易</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Markdown表格: （六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例, 比例合计95.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>0</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>共青城泽升</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Markdown表格: （六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例, 比例合计95.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>0</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>金浦临港基金</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Markdown表格: （六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例, 比例合计95.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>金浦科创基金</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Markdown表格: （六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例, 比例合计95.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>0</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>达晨创联基金</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Markdown表格: （六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例, 比例合计95.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>0</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>财投晨源</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Markdown表格: （六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例, 比例合计95.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>0</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>深圳达晨创程</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Markdown表格: （六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例, 比例合计95.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>0</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>杭州达晨创程</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Markdown表格: （六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例, 比例合计95.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>0</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>达晨财智</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Markdown表格: （六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例, 比例合计95.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>0</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>财智创赢</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Markdown表格: （六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例, 比例合计95.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>0</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>达晨财汇</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Markdown表格: （六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例, 比例合计95.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>0</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>杉晖创业</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Markdown表格: （六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例, 比例合计95.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>0</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>（六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>杉创智至</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Markdown表格: （六）股东私募投资基金备案情况 | （七）本次发行前各股东间的关联关系、一致行动关系及关联股东的各自持股比例, 比例合计95.7%</t>
         </is>
       </c>
     </row>
